--- a/assets/account_import.xlsx
+++ b/assets/account_import.xlsx
@@ -68,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -120,6 +164,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,7 +585,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>行動電話</t>
+          <t>手機</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -786,7 +832,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>行動電話</t>
+          <t>手機</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -954,6 +1000,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -977,18 +1024,18 @@
           <t>格式規則</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="10" t="n"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>數字代碼說明</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1006,14 +1053,14 @@
           <t>僅英文字母與數字，最多 50 字；不可與現有帳號重複</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="10" t="n"/>
       <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1031,14 +1078,14 @@
           <t>最多 50 字</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="10" t="n"/>
       <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1056,14 +1103,14 @@
           <t>需為系統中已存在的部門名稱，最多 15 字</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="10" t="n"/>
       <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1081,18 +1128,18 @@
           <t>只接受 0 或 1</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="10" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>1 = 部門管理員／0 = 一般使用者（企業管理員為母帳號，不可透過匯入建立）</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1110,14 +1157,14 @@
           <t>8～16 碼，須同時包含大寫英文、小寫英文與數字</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="10" t="n"/>
       <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1135,14 +1182,14 @@
           <t>最多 50 字</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="10" t="n"/>
       <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1160,23 +1207,23 @@
           <t>填國碼數字，不含 + 號</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="10" t="n"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
           <t>台灣 886／中國 86／香港 852／澳門 853／日本 81／韓國 82／新加坡 65</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>行動電話</t>
+          <t>手機</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1189,14 +1236,14 @@
           <t>純號碼，不含國碼與 + 號。台灣門號請填去掉開頭 0 的 9 碼（0912345678 → 912345678，含 0 的寫法系統也會自動處理）</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="10" t="n"/>
       <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1214,14 +1261,14 @@
           <t>需為有效的 E-mail 格式</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="10" t="n"/>
       <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1239,18 +1286,18 @@
           <t>只接受 0 或 1，留空預設為 0</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="10" t="n"/>
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t>1 = 開啟／0 = 關閉</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1268,19 +1315,20 @@
           <t>只接受 0 或 1，留空預設為 1</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="10" t="n"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
           <t>1 = 啟用／0 = 停用</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-    </row>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="10" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -1309,6 +1357,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -1319,7 +1368,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>1. 帳號、姓名、部門、角色、密碼、國碼、行動電話、電子信箱 為必填欄位。</t>
+          <t>1. 帳號、姓名、部門、角色、密碼、國碼、手機、電子信箱 為必填欄位。</t>
         </is>
       </c>
     </row>
